--- a/files/exports/it/financings_32_budgetT.xlsx
+++ b/files/exports/it/financings_32_budgetT.xlsx
@@ -354,17 +354,17 @@
   <sheetPr>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:P2"/>
+  <dimension ref="A1:P4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="18"/>
   <cols>
     <col width="30.800000000000004" min="1" max="1" bestFit="1" customWidth="1"/>
     <col width="205.70000000000002" min="2" max="2" bestFit="1" customWidth="1"/>
     <col width="14.3" min="3" max="3" bestFit="1" customWidth="1"/>
     <col width="29.7" min="4" max="4" bestFit="1" customWidth="1"/>
-    <col width="24.75" min="5" max="5" bestFit="1" customWidth="1"/>
+    <col width="41.800000000000004" min="5" max="5" bestFit="1" customWidth="1"/>
     <col width="45.1" min="6" max="6" bestFit="1" customWidth="1"/>
     <col width="23.099999999999998" min="7" max="7" bestFit="1" customWidth="1"/>
-    <col width="52.800000000000004" min="8" max="8" bestFit="1" customWidth="1"/>
+    <col width="53.900000000000006" min="8" max="8" bestFit="1" customWidth="1"/>
     <col width="31.349999999999998" min="9" max="9" bestFit="1" customWidth="1"/>
     <col width="47.300000000000004" min="10" max="10" bestFit="1" customWidth="1"/>
     <col width="66.0" min="11" max="11" bestFit="1" customWidth="1"/>
@@ -459,7 +459,7 @@
     </row>
     <row r="2">
       <c r="A2" s="3">
-        <v>46239.593539754285</v>
+        <v>46248.411581084365</v>
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
@@ -470,11 +470,11 @@
         <v>46292.0</v>
       </c>
       <c r="D2" s="6" t="n">
-        <v>461</v>
+        <v>263</v>
       </c>
       <c r="E2" s="4" t="inlineStr">
         <is>
-          <t>Agri Médias</t>
+          <t>Unione Svizzera dei Contadini (USC)</t>
         </is>
       </c>
       <c r="F2" s="4" t="inlineStr">
@@ -483,7 +483,7 @@
         </is>
       </c>
       <c r="G2" s="6" t="n">
-        <v>601</v>
+        <v>597</v>
       </c>
       <c r="H2" s="4" t="inlineStr">
         <is>
@@ -491,7 +491,7 @@
         </is>
       </c>
       <c r="I2" s="6" t="n">
-        <v>1558</v>
+        <v>1537</v>
       </c>
       <c r="J2" s="4" t="inlineStr">
         <is>
@@ -499,13 +499,13 @@
         </is>
       </c>
       <c r="K2" s="7" t="n">
-        <v>100000.0</v>
+        <v>1531446.0</v>
       </c>
       <c r="L2" s="7" t="n">
-        <v>100000.0</v>
+        <v>1381446.0</v>
       </c>
       <c r="M2" s="7" t="n">
-        <v>0.0</v>
+        <v>150000.0</v>
       </c>
       <c r="N2" s="7" t="n">
         <v>0.0</v>
@@ -514,6 +514,126 @@
         <v>0.0</v>
       </c>
       <c r="P2" s="7" t="n">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3">
+        <v>46248.411581090404</v>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>Per un’alimentazione sicura – mediante il rafforzamento di una produzione nazionale sostenibile, più derrate alimentari vegetali e acqua potabile pulita (Iniziativa sull’alimentazione)</t>
+        </is>
+      </c>
+      <c r="C3" s="5">
+        <v>46292.0</v>
+      </c>
+      <c r="D3" s="6" t="n">
+        <v>461</v>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>Agri Médias Sàrl</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>Persona giuridica o società di persone</t>
+        </is>
+      </c>
+      <c r="G3" s="6" t="n">
+        <v>601</v>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
+          <t>Rifiuto dell'oggetto della votazione popolare</t>
+        </is>
+      </c>
+      <c r="I3" s="6" t="n">
+        <v>1558</v>
+      </c>
+      <c r="J3" s="4" t="inlineStr">
+        <is>
+          <t>Comunicazione delle entrate preventivate</t>
+        </is>
+      </c>
+      <c r="K3" s="7" t="n">
+        <v>100000.0</v>
+      </c>
+      <c r="L3" s="7" t="n">
+        <v>100000.0</v>
+      </c>
+      <c r="M3" s="7" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="N3" s="7" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O3" s="7" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="P3" s="7" t="n">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3">
+        <v>46248.41158109235</v>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>Per un’alimentazione sicura – mediante il rafforzamento di una produzione nazionale sostenibile, più derrate alimentari vegetali e acqua potabile pulita (Iniziativa sull’alimentazione)</t>
+        </is>
+      </c>
+      <c r="C4" s="5">
+        <v>46292.0</v>
+      </c>
+      <c r="D4" s="6" t="n">
+        <v>450</v>
+      </c>
+      <c r="E4" s="4" t="inlineStr">
+        <is>
+          <t>Verein Sauberes Wasser für alle</t>
+        </is>
+      </c>
+      <c r="F4" s="4" t="inlineStr">
+        <is>
+          <t>Persona giuridica o società di persone</t>
+        </is>
+      </c>
+      <c r="G4" s="6" t="n">
+        <v>604</v>
+      </c>
+      <c r="H4" s="4" t="inlineStr">
+        <is>
+          <t>Adozione dell'oggetto della votazione popolare</t>
+        </is>
+      </c>
+      <c r="I4" s="6" t="n">
+        <v>1572</v>
+      </c>
+      <c r="J4" s="4" t="inlineStr">
+        <is>
+          <t>Comunicazione delle entrate preventivate</t>
+        </is>
+      </c>
+      <c r="K4" s="7" t="n">
+        <v>720000.0</v>
+      </c>
+      <c r="L4" s="7" t="n">
+        <v>720000.0</v>
+      </c>
+      <c r="M4" s="7" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="N4" s="7" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O4" s="7" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="P4" s="7" t="n">
         <v>0.0</v>
       </c>
     </row>
@@ -531,17 +651,17 @@
   <sheetPr>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:V3"/>
+  <dimension ref="A1:V15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="18"/>
   <cols>
     <col width="30.800000000000004" min="1" max="1" bestFit="1" customWidth="1"/>
     <col width="205.70000000000002" min="2" max="2" bestFit="1" customWidth="1"/>
     <col width="14.3" min="3" max="3" bestFit="1" customWidth="1"/>
     <col width="29.7" min="4" max="4" bestFit="1" customWidth="1"/>
-    <col width="24.75" min="5" max="5" bestFit="1" customWidth="1"/>
+    <col width="41.800000000000004" min="5" max="5" bestFit="1" customWidth="1"/>
     <col width="45.1" min="6" max="6" bestFit="1" customWidth="1"/>
     <col width="23.099999999999998" min="7" max="7" bestFit="1" customWidth="1"/>
-    <col width="52.800000000000004" min="8" max="8" bestFit="1" customWidth="1"/>
+    <col width="53.900000000000006" min="8" max="8" bestFit="1" customWidth="1"/>
     <col width="31.349999999999998" min="9" max="9" bestFit="1" customWidth="1"/>
     <col width="62.7" min="10" max="10" bestFit="1" customWidth="1"/>
     <col width="26.4" min="11" max="11" bestFit="1" customWidth="1"/>
@@ -672,7 +792,7 @@
     </row>
     <row r="2">
       <c r="A2" s="3">
-        <v>46239.59353975852</v>
+        <v>46248.41158109481</v>
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
@@ -683,11 +803,11 @@
         <v>46292.0</v>
       </c>
       <c r="D2" s="6" t="n">
-        <v>461</v>
+        <v>263</v>
       </c>
       <c r="E2" s="4" t="inlineStr">
         <is>
-          <t>Agri Médias</t>
+          <t>Unione Svizzera dei Contadini (USC)</t>
         </is>
       </c>
       <c r="F2" s="4" t="inlineStr">
@@ -696,7 +816,7 @@
         </is>
       </c>
       <c r="G2" s="6" t="n">
-        <v>601</v>
+        <v>597</v>
       </c>
       <c r="H2" s="4" t="inlineStr">
         <is>
@@ -704,7 +824,7 @@
         </is>
       </c>
       <c r="I2" s="6" t="n">
-        <v>1559</v>
+        <v>1551</v>
       </c>
       <c r="J2" s="4" t="inlineStr">
         <is>
@@ -712,7 +832,7 @@
         </is>
       </c>
       <c r="K2" s="6" t="n">
-        <v>4546</v>
+        <v>4554</v>
       </c>
       <c r="L2" s="4"/>
       <c r="M2" s="4"/>
@@ -720,12 +840,12 @@
       <c r="O2" s="4"/>
       <c r="P2" s="4" t="inlineStr">
         <is>
-          <t>Prométerre</t>
+          <t>BO Milch</t>
         </is>
       </c>
       <c r="Q2" s="4" t="inlineStr">
         <is>
-          <t>Lausanne</t>
+          <t>Bern</t>
         </is>
       </c>
       <c r="R2" s="4" t="inlineStr">
@@ -736,15 +856,15 @@
       <c r="S2" s="4"/>
       <c r="T2" s="4"/>
       <c r="U2" s="7" t="n">
-        <v>50000.0</v>
+        <v>100000.0</v>
       </c>
       <c r="V2" s="5">
-        <v>46178.0</v>
+        <v>46135.0</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3">
-        <v>46239.59353976033</v>
+        <v>46248.41158109635</v>
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
@@ -755,11 +875,11 @@
         <v>46292.0</v>
       </c>
       <c r="D3" s="6" t="n">
-        <v>461</v>
+        <v>263</v>
       </c>
       <c r="E3" s="4" t="inlineStr">
         <is>
-          <t>Agri Médias</t>
+          <t>Unione Svizzera dei Contadini (USC)</t>
         </is>
       </c>
       <c r="F3" s="4" t="inlineStr">
@@ -768,7 +888,7 @@
         </is>
       </c>
       <c r="G3" s="6" t="n">
-        <v>601</v>
+        <v>597</v>
       </c>
       <c r="H3" s="4" t="inlineStr">
         <is>
@@ -776,7 +896,7 @@
         </is>
       </c>
       <c r="I3" s="6" t="n">
-        <v>1559</v>
+        <v>1551</v>
       </c>
       <c r="J3" s="4" t="inlineStr">
         <is>
@@ -784,7 +904,7 @@
         </is>
       </c>
       <c r="K3" s="6" t="n">
-        <v>4547</v>
+        <v>4555</v>
       </c>
       <c r="L3" s="4"/>
       <c r="M3" s="4"/>
@@ -792,12 +912,12 @@
       <c r="O3" s="4"/>
       <c r="P3" s="4" t="inlineStr">
         <is>
-          <t>AgorA</t>
+          <t>Vereinigung der Schweizerischen Milchindustrie</t>
         </is>
       </c>
       <c r="Q3" s="4" t="inlineStr">
         <is>
-          <t>Lausanne</t>
+          <t>Bern</t>
         </is>
       </c>
       <c r="R3" s="4" t="inlineStr">
@@ -808,10 +928,890 @@
       <c r="S3" s="4"/>
       <c r="T3" s="4"/>
       <c r="U3" s="7" t="n">
+        <v>60000.0</v>
+      </c>
+      <c r="V3" s="5">
+        <v>46209.0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3">
+        <v>46248.41158109751</v>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>Per un’alimentazione sicura – mediante il rafforzamento di una produzione nazionale sostenibile, più derrate alimentari vegetali e acqua potabile pulita (Iniziativa sull’alimentazione)</t>
+        </is>
+      </c>
+      <c r="C4" s="5">
+        <v>46292.0</v>
+      </c>
+      <c r="D4" s="6" t="n">
+        <v>263</v>
+      </c>
+      <c r="E4" s="4" t="inlineStr">
+        <is>
+          <t>Unione Svizzera dei Contadini (USC)</t>
+        </is>
+      </c>
+      <c r="F4" s="4" t="inlineStr">
+        <is>
+          <t>Persona giuridica o società di persone</t>
+        </is>
+      </c>
+      <c r="G4" s="6" t="n">
+        <v>597</v>
+      </c>
+      <c r="H4" s="4" t="inlineStr">
+        <is>
+          <t>Rifiuto dell'oggetto della votazione popolare</t>
+        </is>
+      </c>
+      <c r="I4" s="6" t="n">
+        <v>1551</v>
+      </c>
+      <c r="J4" s="4" t="inlineStr">
+        <is>
+          <t>Comunicazione di liberalità superiori a 15 000 franchi</t>
+        </is>
+      </c>
+      <c r="K4" s="6" t="n">
+        <v>4556</v>
+      </c>
+      <c r="L4" s="4"/>
+      <c r="M4" s="4"/>
+      <c r="N4" s="4"/>
+      <c r="O4" s="4"/>
+      <c r="P4" s="4" t="inlineStr">
+        <is>
+          <t>Fromarte</t>
+        </is>
+      </c>
+      <c r="Q4" s="4" t="inlineStr">
+        <is>
+          <t>Bern</t>
+        </is>
+      </c>
+      <c r="R4" s="4" t="inlineStr">
+        <is>
+          <t>Monetaria</t>
+        </is>
+      </c>
+      <c r="S4" s="4"/>
+      <c r="T4" s="4"/>
+      <c r="U4" s="7" t="n">
+        <v>40000.0</v>
+      </c>
+      <c r="V4" s="5">
+        <v>46133.0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3">
+        <v>46248.41158109848</v>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>Per un’alimentazione sicura – mediante il rafforzamento di una produzione nazionale sostenibile, più derrate alimentari vegetali e acqua potabile pulita (Iniziativa sull’alimentazione)</t>
+        </is>
+      </c>
+      <c r="C5" s="5">
+        <v>46292.0</v>
+      </c>
+      <c r="D5" s="6" t="n">
+        <v>263</v>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>Unione Svizzera dei Contadini (USC)</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>Persona giuridica o società di persone</t>
+        </is>
+      </c>
+      <c r="G5" s="6" t="n">
+        <v>597</v>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
+        <is>
+          <t>Rifiuto dell'oggetto della votazione popolare</t>
+        </is>
+      </c>
+      <c r="I5" s="6" t="n">
+        <v>1551</v>
+      </c>
+      <c r="J5" s="4" t="inlineStr">
+        <is>
+          <t>Comunicazione di liberalità superiori a 15 000 franchi</t>
+        </is>
+      </c>
+      <c r="K5" s="6" t="n">
+        <v>4557</v>
+      </c>
+      <c r="L5" s="4"/>
+      <c r="M5" s="4"/>
+      <c r="N5" s="4"/>
+      <c r="O5" s="4"/>
+      <c r="P5" s="4" t="inlineStr">
+        <is>
+          <t>Schweizer Milchproduzenten</t>
+        </is>
+      </c>
+      <c r="Q5" s="4" t="inlineStr">
+        <is>
+          <t>Bern</t>
+        </is>
+      </c>
+      <c r="R5" s="4" t="inlineStr">
+        <is>
+          <t>Monetaria</t>
+        </is>
+      </c>
+      <c r="S5" s="4"/>
+      <c r="T5" s="4"/>
+      <c r="U5" s="7" t="n">
+        <v>350000.0</v>
+      </c>
+      <c r="V5" s="5">
+        <v>46114.0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3">
+        <v>46248.41158109942</v>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>Per un’alimentazione sicura – mediante il rafforzamento di una produzione nazionale sostenibile, più derrate alimentari vegetali e acqua potabile pulita (Iniziativa sull’alimentazione)</t>
+        </is>
+      </c>
+      <c r="C6" s="5">
+        <v>46292.0</v>
+      </c>
+      <c r="D6" s="6" t="n">
+        <v>263</v>
+      </c>
+      <c r="E6" s="4" t="inlineStr">
+        <is>
+          <t>Unione Svizzera dei Contadini (USC)</t>
+        </is>
+      </c>
+      <c r="F6" s="4" t="inlineStr">
+        <is>
+          <t>Persona giuridica o società di persone</t>
+        </is>
+      </c>
+      <c r="G6" s="6" t="n">
+        <v>597</v>
+      </c>
+      <c r="H6" s="4" t="inlineStr">
+        <is>
+          <t>Rifiuto dell'oggetto della votazione popolare</t>
+        </is>
+      </c>
+      <c r="I6" s="6" t="n">
+        <v>1551</v>
+      </c>
+      <c r="J6" s="4" t="inlineStr">
+        <is>
+          <t>Comunicazione di liberalità superiori a 15 000 franchi</t>
+        </is>
+      </c>
+      <c r="K6" s="6" t="n">
+        <v>4558</v>
+      </c>
+      <c r="L6" s="4"/>
+      <c r="M6" s="4"/>
+      <c r="N6" s="4"/>
+      <c r="O6" s="4"/>
+      <c r="P6" s="4" t="inlineStr">
+        <is>
+          <t>Gastrosuisse</t>
+        </is>
+      </c>
+      <c r="Q6" s="4" t="inlineStr">
+        <is>
+          <t>Zürich</t>
+        </is>
+      </c>
+      <c r="R6" s="4" t="inlineStr">
+        <is>
+          <t>Monetaria</t>
+        </is>
+      </c>
+      <c r="S6" s="4"/>
+      <c r="T6" s="4"/>
+      <c r="U6" s="7" t="n">
+        <v>120000.0</v>
+      </c>
+      <c r="V6" s="5">
+        <v>46114.0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3">
+        <v>46248.41158110034</v>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>Per un’alimentazione sicura – mediante il rafforzamento di una produzione nazionale sostenibile, più derrate alimentari vegetali e acqua potabile pulita (Iniziativa sull’alimentazione)</t>
+        </is>
+      </c>
+      <c r="C7" s="5">
+        <v>46292.0</v>
+      </c>
+      <c r="D7" s="6" t="n">
+        <v>263</v>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>Unione Svizzera dei Contadini (USC)</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>Persona giuridica o società di persone</t>
+        </is>
+      </c>
+      <c r="G7" s="6" t="n">
+        <v>597</v>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
+        <is>
+          <t>Rifiuto dell'oggetto della votazione popolare</t>
+        </is>
+      </c>
+      <c r="I7" s="6" t="n">
+        <v>1551</v>
+      </c>
+      <c r="J7" s="4" t="inlineStr">
+        <is>
+          <t>Comunicazione di liberalità superiori a 15 000 franchi</t>
+        </is>
+      </c>
+      <c r="K7" s="6" t="n">
+        <v>4559</v>
+      </c>
+      <c r="L7" s="4"/>
+      <c r="M7" s="4"/>
+      <c r="N7" s="4"/>
+      <c r="O7" s="4"/>
+      <c r="P7" s="4" t="inlineStr">
+        <is>
+          <t>Gallosuisse</t>
+        </is>
+      </c>
+      <c r="Q7" s="4" t="inlineStr">
+        <is>
+          <t>Zollikofen</t>
+        </is>
+      </c>
+      <c r="R7" s="4" t="inlineStr">
+        <is>
+          <t>Monetaria</t>
+        </is>
+      </c>
+      <c r="S7" s="4"/>
+      <c r="T7" s="4"/>
+      <c r="U7" s="7" t="n">
+        <v>58500.0</v>
+      </c>
+      <c r="V7" s="5">
+        <v>46170.0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="3">
+        <v>46248.411581101376</v>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>Per un’alimentazione sicura – mediante il rafforzamento di una produzione nazionale sostenibile, più derrate alimentari vegetali e acqua potabile pulita (Iniziativa sull’alimentazione)</t>
+        </is>
+      </c>
+      <c r="C8" s="5">
+        <v>46292.0</v>
+      </c>
+      <c r="D8" s="6" t="n">
+        <v>263</v>
+      </c>
+      <c r="E8" s="4" t="inlineStr">
+        <is>
+          <t>Unione Svizzera dei Contadini (USC)</t>
+        </is>
+      </c>
+      <c r="F8" s="4" t="inlineStr">
+        <is>
+          <t>Persona giuridica o società di persone</t>
+        </is>
+      </c>
+      <c r="G8" s="6" t="n">
+        <v>597</v>
+      </c>
+      <c r="H8" s="4" t="inlineStr">
+        <is>
+          <t>Rifiuto dell'oggetto della votazione popolare</t>
+        </is>
+      </c>
+      <c r="I8" s="6" t="n">
+        <v>1551</v>
+      </c>
+      <c r="J8" s="4" t="inlineStr">
+        <is>
+          <t>Comunicazione di liberalità superiori a 15 000 franchi</t>
+        </is>
+      </c>
+      <c r="K8" s="6" t="n">
+        <v>4560</v>
+      </c>
+      <c r="L8" s="4"/>
+      <c r="M8" s="4"/>
+      <c r="N8" s="4"/>
+      <c r="O8" s="4"/>
+      <c r="P8" s="4" t="inlineStr">
+        <is>
+          <t>Proviande</t>
+        </is>
+      </c>
+      <c r="Q8" s="4" t="inlineStr">
+        <is>
+          <t>Bern</t>
+        </is>
+      </c>
+      <c r="R8" s="4" t="inlineStr">
+        <is>
+          <t>Monetaria</t>
+        </is>
+      </c>
+      <c r="S8" s="4"/>
+      <c r="T8" s="4"/>
+      <c r="U8" s="7" t="n">
+        <v>600000.0</v>
+      </c>
+      <c r="V8" s="5">
+        <v>46202.0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3">
+        <v>46248.411581102315</v>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>Per un’alimentazione sicura – mediante il rafforzamento di una produzione nazionale sostenibile, più derrate alimentari vegetali e acqua potabile pulita (Iniziativa sull’alimentazione)</t>
+        </is>
+      </c>
+      <c r="C9" s="5">
+        <v>46292.0</v>
+      </c>
+      <c r="D9" s="6" t="n">
+        <v>263</v>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>Unione Svizzera dei Contadini (USC)</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>Persona giuridica o società di persone</t>
+        </is>
+      </c>
+      <c r="G9" s="6" t="n">
+        <v>597</v>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
+        <is>
+          <t>Rifiuto dell'oggetto della votazione popolare</t>
+        </is>
+      </c>
+      <c r="I9" s="6" t="n">
+        <v>1551</v>
+      </c>
+      <c r="J9" s="4" t="inlineStr">
+        <is>
+          <t>Comunicazione di liberalità superiori a 15 000 franchi</t>
+        </is>
+      </c>
+      <c r="K9" s="6" t="n">
+        <v>4561</v>
+      </c>
+      <c r="L9" s="4"/>
+      <c r="M9" s="4"/>
+      <c r="N9" s="4"/>
+      <c r="O9" s="4"/>
+      <c r="P9" s="4" t="inlineStr">
+        <is>
+          <t>Arbeitsgemeinschaft Schweizerischer Rinderzüchter</t>
+        </is>
+      </c>
+      <c r="Q9" s="4" t="inlineStr">
+        <is>
+          <t>Zollikofen</t>
+        </is>
+      </c>
+      <c r="R9" s="4" t="inlineStr">
+        <is>
+          <t>Monetaria</t>
+        </is>
+      </c>
+      <c r="S9" s="4"/>
+      <c r="T9" s="4"/>
+      <c r="U9" s="7" t="n">
+        <v>15000.0</v>
+      </c>
+      <c r="V9" s="5">
+        <v>46043.0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="3">
+        <v>46248.41158110352</v>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>Per un’alimentazione sicura – mediante il rafforzamento di una produzione nazionale sostenibile, più derrate alimentari vegetali e acqua potabile pulita (Iniziativa sull’alimentazione)</t>
+        </is>
+      </c>
+      <c r="C10" s="5">
+        <v>46292.0</v>
+      </c>
+      <c r="D10" s="6" t="n">
+        <v>263</v>
+      </c>
+      <c r="E10" s="4" t="inlineStr">
+        <is>
+          <t>Unione Svizzera dei Contadini (USC)</t>
+        </is>
+      </c>
+      <c r="F10" s="4" t="inlineStr">
+        <is>
+          <t>Persona giuridica o società di persone</t>
+        </is>
+      </c>
+      <c r="G10" s="6" t="n">
+        <v>597</v>
+      </c>
+      <c r="H10" s="4" t="inlineStr">
+        <is>
+          <t>Rifiuto dell'oggetto della votazione popolare</t>
+        </is>
+      </c>
+      <c r="I10" s="6" t="n">
+        <v>1551</v>
+      </c>
+      <c r="J10" s="4" t="inlineStr">
+        <is>
+          <t>Comunicazione di liberalità superiori a 15 000 franchi</t>
+        </is>
+      </c>
+      <c r="K10" s="6" t="n">
+        <v>4562</v>
+      </c>
+      <c r="L10" s="4"/>
+      <c r="M10" s="4"/>
+      <c r="N10" s="4"/>
+      <c r="O10" s="4"/>
+      <c r="P10" s="4" t="inlineStr">
+        <is>
+          <t>Schweizer Bauernverband</t>
+        </is>
+      </c>
+      <c r="Q10" s="4" t="inlineStr">
+        <is>
+          <t>Brugg</t>
+        </is>
+      </c>
+      <c r="R10" s="4" t="inlineStr">
+        <is>
+          <t>Non monetaria</t>
+        </is>
+      </c>
+      <c r="S10" s="4" t="inlineStr">
+        <is>
+          <t>Prestazione in natura</t>
+        </is>
+      </c>
+      <c r="T10" s="4" t="inlineStr">
+        <is>
+          <t>Arbeitsaufwand</t>
+        </is>
+      </c>
+      <c r="U10" s="7" t="n">
+        <v>150000.0</v>
+      </c>
+      <c r="V10" s="5">
+        <v>46245.0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3">
+        <v>46248.41158110464</v>
+      </c>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>Per un’alimentazione sicura – mediante il rafforzamento di una produzione nazionale sostenibile, più derrate alimentari vegetali e acqua potabile pulita (Iniziativa sull’alimentazione)</t>
+        </is>
+      </c>
+      <c r="C11" s="5">
+        <v>46292.0</v>
+      </c>
+      <c r="D11" s="6" t="n">
+        <v>461</v>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>Agri Médias Sàrl</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>Persona giuridica o società di persone</t>
+        </is>
+      </c>
+      <c r="G11" s="6" t="n">
+        <v>601</v>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
+        <is>
+          <t>Rifiuto dell'oggetto della votazione popolare</t>
+        </is>
+      </c>
+      <c r="I11" s="6" t="n">
+        <v>1559</v>
+      </c>
+      <c r="J11" s="4" t="inlineStr">
+        <is>
+          <t>Comunicazione di liberalità superiori a 15 000 franchi</t>
+        </is>
+      </c>
+      <c r="K11" s="6" t="n">
+        <v>4546</v>
+      </c>
+      <c r="L11" s="4"/>
+      <c r="M11" s="4"/>
+      <c r="N11" s="4"/>
+      <c r="O11" s="4"/>
+      <c r="P11" s="4" t="inlineStr">
+        <is>
+          <t>Prométerre</t>
+        </is>
+      </c>
+      <c r="Q11" s="4" t="inlineStr">
+        <is>
+          <t>Lausanne</t>
+        </is>
+      </c>
+      <c r="R11" s="4" t="inlineStr">
+        <is>
+          <t>Monetaria</t>
+        </is>
+      </c>
+      <c r="S11" s="4"/>
+      <c r="T11" s="4"/>
+      <c r="U11" s="7" t="n">
         <v>50000.0</v>
       </c>
-      <c r="V3" s="5">
+      <c r="V11" s="5">
         <v>46178.0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="3">
+        <v>46248.411581105705</v>
+      </c>
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t>Per un’alimentazione sicura – mediante il rafforzamento di una produzione nazionale sostenibile, più derrate alimentari vegetali e acqua potabile pulita (Iniziativa sull’alimentazione)</t>
+        </is>
+      </c>
+      <c r="C12" s="5">
+        <v>46292.0</v>
+      </c>
+      <c r="D12" s="6" t="n">
+        <v>461</v>
+      </c>
+      <c r="E12" s="4" t="inlineStr">
+        <is>
+          <t>Agri Médias Sàrl</t>
+        </is>
+      </c>
+      <c r="F12" s="4" t="inlineStr">
+        <is>
+          <t>Persona giuridica o società di persone</t>
+        </is>
+      </c>
+      <c r="G12" s="6" t="n">
+        <v>601</v>
+      </c>
+      <c r="H12" s="4" t="inlineStr">
+        <is>
+          <t>Rifiuto dell'oggetto della votazione popolare</t>
+        </is>
+      </c>
+      <c r="I12" s="6" t="n">
+        <v>1559</v>
+      </c>
+      <c r="J12" s="4" t="inlineStr">
+        <is>
+          <t>Comunicazione di liberalità superiori a 15 000 franchi</t>
+        </is>
+      </c>
+      <c r="K12" s="6" t="n">
+        <v>4547</v>
+      </c>
+      <c r="L12" s="4"/>
+      <c r="M12" s="4"/>
+      <c r="N12" s="4"/>
+      <c r="O12" s="4"/>
+      <c r="P12" s="4" t="inlineStr">
+        <is>
+          <t>AgorA</t>
+        </is>
+      </c>
+      <c r="Q12" s="4" t="inlineStr">
+        <is>
+          <t>Lausanne</t>
+        </is>
+      </c>
+      <c r="R12" s="4" t="inlineStr">
+        <is>
+          <t>Monetaria</t>
+        </is>
+      </c>
+      <c r="S12" s="4"/>
+      <c r="T12" s="4"/>
+      <c r="U12" s="7" t="n">
+        <v>50000.0</v>
+      </c>
+      <c r="V12" s="5">
+        <v>46178.0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3">
+        <v>46248.411581106695</v>
+      </c>
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>Per un’alimentazione sicura – mediante il rafforzamento di una produzione nazionale sostenibile, più derrate alimentari vegetali e acqua potabile pulita (Iniziativa sull’alimentazione)</t>
+        </is>
+      </c>
+      <c r="C13" s="5">
+        <v>46292.0</v>
+      </c>
+      <c r="D13" s="6" t="n">
+        <v>450</v>
+      </c>
+      <c r="E13" s="4" t="inlineStr">
+        <is>
+          <t>Verein Sauberes Wasser für alle</t>
+        </is>
+      </c>
+      <c r="F13" s="4" t="inlineStr">
+        <is>
+          <t>Persona giuridica o società di persone</t>
+        </is>
+      </c>
+      <c r="G13" s="6" t="n">
+        <v>604</v>
+      </c>
+      <c r="H13" s="4" t="inlineStr">
+        <is>
+          <t>Adozione dell'oggetto della votazione popolare</t>
+        </is>
+      </c>
+      <c r="I13" s="6" t="n">
+        <v>1575</v>
+      </c>
+      <c r="J13" s="4" t="inlineStr">
+        <is>
+          <t>Comunicazione di liberalità superiori a 15 000 franchi</t>
+        </is>
+      </c>
+      <c r="K13" s="6" t="n">
+        <v>4567</v>
+      </c>
+      <c r="L13" s="4"/>
+      <c r="M13" s="4"/>
+      <c r="N13" s="4"/>
+      <c r="O13" s="4"/>
+      <c r="P13" s="4" t="inlineStr">
+        <is>
+          <t>Visempio Stiftung</t>
+        </is>
+      </c>
+      <c r="Q13" s="4" t="inlineStr">
+        <is>
+          <t>8805 Richterswil</t>
+        </is>
+      </c>
+      <c r="R13" s="4" t="inlineStr">
+        <is>
+          <t>Monetaria</t>
+        </is>
+      </c>
+      <c r="S13" s="4"/>
+      <c r="T13" s="4"/>
+      <c r="U13" s="7" t="n">
+        <v>205000.0</v>
+      </c>
+      <c r="V13" s="5">
+        <v>46224.0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="3">
+        <v>46248.41158110782</v>
+      </c>
+      <c r="B14" s="4" t="inlineStr">
+        <is>
+          <t>Per un’alimentazione sicura – mediante il rafforzamento di una produzione nazionale sostenibile, più derrate alimentari vegetali e acqua potabile pulita (Iniziativa sull’alimentazione)</t>
+        </is>
+      </c>
+      <c r="C14" s="5">
+        <v>46292.0</v>
+      </c>
+      <c r="D14" s="6" t="n">
+        <v>450</v>
+      </c>
+      <c r="E14" s="4" t="inlineStr">
+        <is>
+          <t>Verein Sauberes Wasser für alle</t>
+        </is>
+      </c>
+      <c r="F14" s="4" t="inlineStr">
+        <is>
+          <t>Persona giuridica o società di persone</t>
+        </is>
+      </c>
+      <c r="G14" s="6" t="n">
+        <v>604</v>
+      </c>
+      <c r="H14" s="4" t="inlineStr">
+        <is>
+          <t>Adozione dell'oggetto della votazione popolare</t>
+        </is>
+      </c>
+      <c r="I14" s="6" t="n">
+        <v>1575</v>
+      </c>
+      <c r="J14" s="4" t="inlineStr">
+        <is>
+          <t>Comunicazione di liberalità superiori a 15 000 franchi</t>
+        </is>
+      </c>
+      <c r="K14" s="6" t="n">
+        <v>4586</v>
+      </c>
+      <c r="L14" s="4" t="inlineStr">
+        <is>
+          <t>Kummer</t>
+        </is>
+      </c>
+      <c r="M14" s="4" t="inlineStr">
+        <is>
+          <t>Walter</t>
+        </is>
+      </c>
+      <c r="N14" s="4" t="inlineStr">
+        <is>
+          <t>4539 Rumsiberg</t>
+        </is>
+      </c>
+      <c r="O14" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="P14" s="4"/>
+      <c r="Q14" s="4"/>
+      <c r="R14" s="4" t="inlineStr">
+        <is>
+          <t>Monetaria</t>
+        </is>
+      </c>
+      <c r="S14" s="4"/>
+      <c r="T14" s="4"/>
+      <c r="U14" s="7" t="n">
+        <v>275000.0</v>
+      </c>
+      <c r="V14" s="5">
+        <v>46224.0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="3">
+        <v>46248.41158110888</v>
+      </c>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>Per un’alimentazione sicura – mediante il rafforzamento di una produzione nazionale sostenibile, più derrate alimentari vegetali e acqua potabile pulita (Iniziativa sull’alimentazione)</t>
+        </is>
+      </c>
+      <c r="C15" s="5">
+        <v>46292.0</v>
+      </c>
+      <c r="D15" s="6" t="n">
+        <v>450</v>
+      </c>
+      <c r="E15" s="4" t="inlineStr">
+        <is>
+          <t>Verein Sauberes Wasser für alle</t>
+        </is>
+      </c>
+      <c r="F15" s="4" t="inlineStr">
+        <is>
+          <t>Persona giuridica o società di persone</t>
+        </is>
+      </c>
+      <c r="G15" s="6" t="n">
+        <v>604</v>
+      </c>
+      <c r="H15" s="4" t="inlineStr">
+        <is>
+          <t>Adozione dell'oggetto della votazione popolare</t>
+        </is>
+      </c>
+      <c r="I15" s="6" t="n">
+        <v>1575</v>
+      </c>
+      <c r="J15" s="4" t="inlineStr">
+        <is>
+          <t>Comunicazione di liberalità superiori a 15 000 franchi</t>
+        </is>
+      </c>
+      <c r="K15" s="6" t="n">
+        <v>4590</v>
+      </c>
+      <c r="L15" s="4"/>
+      <c r="M15" s="4"/>
+      <c r="N15" s="4"/>
+      <c r="O15" s="4"/>
+      <c r="P15" s="4" t="inlineStr">
+        <is>
+          <t>Visempio Stiftung</t>
+        </is>
+      </c>
+      <c r="Q15" s="4" t="inlineStr">
+        <is>
+          <t>8805 Richterswil</t>
+        </is>
+      </c>
+      <c r="R15" s="4" t="inlineStr">
+        <is>
+          <t>Monetaria</t>
+        </is>
+      </c>
+      <c r="S15" s="4"/>
+      <c r="T15" s="4"/>
+      <c r="U15" s="7" t="n">
+        <v>200000.0</v>
+      </c>
+      <c r="V15" s="5">
+        <v>46245.0</v>
       </c>
     </row>
   </sheetData>
